--- a/artfynd/A 61981-2025 artfynd.xlsx
+++ b/artfynd/A 61981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62024521</v>
+        <v>96970432</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517554.782355516</v>
+        <v>517385</v>
       </c>
       <c r="R2" t="n">
-        <v>6992309.826134036</v>
+        <v>6992357</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-10-23</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-10-23</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,79 +767,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg, Ulrika Westling</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62024520</v>
+        <v>96631253</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rissna, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517424.4656017528</v>
+        <v>517543</v>
       </c>
       <c r="R3" t="n">
-        <v>6992308.217635215</v>
+        <v>6992330</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-10-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-10-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +864,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>bäckskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg, Ulrika Westling</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -922,12 +883,7 @@
         <v>62024519</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517424.4656017528</v>
+        <v>517424</v>
       </c>
       <c r="R4" t="n">
-        <v>6992308.217635215</v>
+        <v>6992308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +948,9 @@
           <t>2016-10-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-10-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96631254</v>
+        <v>62024520</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,37 +998,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517543.3225567752</v>
+        <v>517424</v>
       </c>
       <c r="R5" t="n">
-        <v>6992329.716769697</v>
+        <v>6992308</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,22 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,69 +1068,74 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>bäckskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Kjetselberg, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96631244</v>
+        <v>62024521</v>
       </c>
       <c r="B6" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517423.6564463805</v>
+        <v>517555</v>
       </c>
       <c r="R6" t="n">
-        <v>6992374.418980608</v>
+        <v>6992310</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,22 +1159,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,69 +1175,75 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Kjetselberg, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96631251</v>
+        <v>96970805</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517562.4404700297</v>
+        <v>517386</v>
       </c>
       <c r="R7" t="n">
-        <v>6992321.204209775</v>
+        <v>6992347</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,22 +1267,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,27 +1297,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96631252</v>
+        <v>96972009</v>
       </c>
       <c r="B8" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,37 +1320,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517562.4404700297</v>
+        <v>517502</v>
       </c>
       <c r="R8" t="n">
-        <v>6992321.204209775</v>
+        <v>6992278</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,22 +1375,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,49 +1405,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96631249</v>
+        <v>96631242</v>
       </c>
       <c r="B9" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517571.458315378</v>
+        <v>517424</v>
       </c>
       <c r="R9" t="n">
-        <v>6992333.043083676</v>
+        <v>6992374</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1562,19 +1485,9 @@
           <t>2021-10-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96631250</v>
+        <v>96970509</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,37 +1525,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517562.4404700297</v>
+        <v>517391</v>
       </c>
       <c r="R10" t="n">
-        <v>6992321.204209775</v>
+        <v>6992354</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,22 +1580,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,65 +1610,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96631253</v>
+        <v>96971950</v>
       </c>
       <c r="B11" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517543.3225567752</v>
+        <v>517485</v>
       </c>
       <c r="R11" t="n">
-        <v>6992329.716769697</v>
+        <v>6992282</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,22 +1688,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,65 +1718,61 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96631243</v>
+        <v>96972249</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517423.6564463805</v>
+        <v>517566</v>
       </c>
       <c r="R12" t="n">
-        <v>6992374.418980608</v>
+        <v>6992326</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,22 +1796,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,27 +1826,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96631255</v>
+        <v>96970528</v>
       </c>
       <c r="B13" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,37 +1849,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rissna öst om Bygdegården, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517543.3225567752</v>
+        <v>517391</v>
       </c>
       <c r="R13" t="n">
-        <v>6992329.716769697</v>
+        <v>6992354</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,22 +1904,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,49 +1934,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96631242</v>
+        <v>96631243</v>
       </c>
       <c r="B14" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517423.6564463805</v>
+        <v>517424</v>
       </c>
       <c r="R14" t="n">
-        <v>6992374.418980608</v>
+        <v>6992374</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2122,19 +2014,9 @@
           <t>2021-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,15 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96970528</v>
+        <v>96631251</v>
       </c>
       <c r="B15" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,38 +2054,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rissna, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517391.0724095266</v>
+        <v>517562</v>
       </c>
       <c r="R15" t="n">
-        <v>6992353.838667472</v>
+        <v>6992321</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2232,22 +2108,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,80 +2128,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96971604</v>
+        <v>96631248</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rissna, Bräcke, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517359.4906166536</v>
+        <v>517598</v>
       </c>
       <c r="R16" t="n">
-        <v>6992315.578743681</v>
+        <v>6992355</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2359,22 +2205,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,63 +2225,72 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96972009</v>
+        <v>96971604</v>
       </c>
       <c r="B17" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rissna, Jmt</t>
+          <t>Rissna, Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517501.8232879099</v>
+        <v>517360</v>
       </c>
       <c r="R17" t="n">
-        <v>6992278.250944679</v>
+        <v>6992315</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2477,7 +2322,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2332,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,15 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96971950</v>
+        <v>96631250</v>
       </c>
       <c r="B18" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,38 +2370,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rissna, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517485.0001165504</v>
+        <v>517562</v>
       </c>
       <c r="R18" t="n">
-        <v>6992282.241608188</v>
+        <v>6992321</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,22 +2424,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,66 +2444,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96970805</v>
+        <v>96631244</v>
       </c>
       <c r="B19" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517386.1139738225</v>
+        <v>517424</v>
       </c>
       <c r="R19" t="n">
-        <v>6992347.010193373</v>
+        <v>6992374</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,22 +2521,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,66 +2541,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96972249</v>
+        <v>96631249</v>
       </c>
       <c r="B20" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rissna, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517566.5002249266</v>
+        <v>517571</v>
       </c>
       <c r="R20" t="n">
-        <v>6992326.214288339</v>
+        <v>6992333</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2811,22 +2618,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,66 +2638,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96970509</v>
+        <v>96631252</v>
       </c>
       <c r="B21" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rissna, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517391.0724095266</v>
+        <v>517562</v>
       </c>
       <c r="R21" t="n">
-        <v>6992353.838667472</v>
+        <v>6992321</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2924,22 +2715,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,66 +2735,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96970432</v>
+        <v>96631255</v>
       </c>
       <c r="B22" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rissna, Jmt</t>
+          <t>Rissna öst om Bygdegården, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517385.1524342854</v>
+        <v>517543</v>
       </c>
       <c r="R22" t="n">
-        <v>6992356.981212624</v>
+        <v>6992330</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3037,22 +2812,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3067,15 +2832,209 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96631254</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rissna öst om Bygdegården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>517543</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6992330</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>96631241</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rissna öst om Bygdegården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>517358</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6992351</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61981-2025 artfynd.xlsx
+++ b/artfynd/A 61981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96970432</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631253</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62024519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62024520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62024521</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96970805</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96972009</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631242</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96970509</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96971950</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1835,6 +1890,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96972249</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96970528</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2040,6 +2105,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631243</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2137,6 +2207,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631251</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2234,6 +2309,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631248</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96971604</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2453,6 +2538,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631250</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2550,6 +2640,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631244</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2647,6 +2742,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631249</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2744,6 +2844,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631252</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2841,6 +2946,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631255</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2938,6 +3048,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631254</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3035,8 +3150,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>